--- a/Extracted_data_analysis/global/Output-Transformed_data/Realm_count.xlsx
+++ b/Extracted_data_analysis/global/Output-Transformed_data/Realm_count.xlsx
@@ -381,7 +381,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -394,7 +394,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="4">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
